--- a/범운해운항공_전체데이터_통합백업_2026-10-20.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-20.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE55"/>
+  <dimension ref="A1:AE57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7251,6 +7251,272 @@
       <c r="AC55" t="inlineStr"/>
       <c r="AD55" t="inlineStr"/>
       <c r="AE55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BW-2026-059</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BW260008</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>텐트러스트</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Jun Cheong</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>주식회사 비에프터</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>45×31×16cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0.022 CBM</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>4</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>154200</v>
+      </c>
+      <c r="U56" t="n">
+        <v>74000</v>
+      </c>
+      <c r="V56" t="n">
+        <v>80200</v>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>5332 Noel Drive Temple City, CA 91780</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>9099922845</t>
+        </is>
+      </c>
+      <c r="AC56" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BW-2026-060</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>BW260009</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>에이블큐인터내셔널</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>杨小羊</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>윤세형</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>해상(LCL)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>필러</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0.000 CBM</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>332</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>332</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>15936000</v>
+      </c>
+      <c r="U57" t="n">
+        <v>12948000</v>
+      </c>
+      <c r="V57" t="n">
+        <v>2988000</v>
+      </c>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湖北省宜昌市秭归县茅坪镇建东大道海辣百川 </t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>19096164768</t>
+        </is>
+      </c>
+      <c r="AC57" t="n">
+        <v>332</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>332</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>332</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7263,7 +7529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7490,6 +7756,31 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>필러 20박스 윤세형 입고비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BFT 점심식사</t>
         </is>
       </c>
     </row>
@@ -7829,7 +8120,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵", "에이블큐인터내셔널"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}, "에이블큐인터내셔널": {"중국": {"해상(LCL)": {"필러": {"기본중량": 1.0, "기본요금": 48000, "추가단가": 48000, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "addtrd@naver.com", "담당자": "박수진", "전화번호": "010-2086-1180", "주소": "서울특별시 강서구 금남화로 287-19,상가1동 2층 208호(방화동,방화5단지아파트)"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "에이블큐인터내셔널": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "서광부장님", "전화번호": "010-6282-1025", "주소": "서울특별시 강서구 양천로24가길28-2"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵", "에이블큐인터내셔널"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}, "에이블큐인터내셔널": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 48000, "추가단가": 48000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 48000, "추가단가": 48000, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "에이블큐인터내셔널": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "서광부장님", "전화번호": "nan", "주소": "서울 강서구 양천로24가길28-2"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "주식회사 비에프터"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "주식회사 비에프터": {"미국": {"항공(Air)": {"기타": {"기본중량": 1.0, "기본요금": 18500, "추가단가": 18500, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "김창화부사장", "전화번호": "010-6774-5216", "주소": "경기도 김포시 고촌읍 전호로 26번길 54 가동"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "주식회사 비에프터": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "김창화부사장", "전화번호": "010-6774-5216", "주소": "경기도 김포시 고촌읍 전호로 26번길 54 가동"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-20.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-20.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE57"/>
+  <dimension ref="A1:AE62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7370,10 +7370,8 @@
           <t>5332 Noel Drive Temple City, CA 91780</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>9099922845</t>
-        </is>
+      <c r="AB56" t="n">
+        <v>9099922845</v>
       </c>
       <c r="AC56" t="n">
         <v>3.45</v>
@@ -7503,10 +7501,8 @@
           <t xml:space="preserve">湖北省宜昌市秭归县茅坪镇建东大道海辣百川 </t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>19096164768</t>
-        </is>
+      <c r="AB57" t="n">
+        <v>19096164768</v>
       </c>
       <c r="AC57" t="n">
         <v>332</v>
@@ -7516,6 +7512,671 @@
       </c>
       <c r="AE57" t="n">
         <v>332</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BW-2026-061</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>BW260010</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Trisha Banusing</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>36×36×18cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0.023 CBM</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>4</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
+        <v>219200</v>
+      </c>
+      <c r="U58" t="n">
+        <v>110000</v>
+      </c>
+      <c r="V58" t="n">
+        <v>109200</v>
+      </c>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>134 S Seneca Circle Anaheim California 92805 USA</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>1 707-685-7724</t>
+        </is>
+      </c>
+      <c r="AC58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BW-2026-062</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BW260011</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Alex Arrieta Lopez</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>49×35×22cm(1CTN) / 49×46×28cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0.102 CBM</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>17</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
+        <v>792640</v>
+      </c>
+      <c r="U59" t="n">
+        <v>435000</v>
+      </c>
+      <c r="V59" t="n">
+        <v>357640</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>화장품 의약품</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>8589 NW 54TH ST MIAMI, FL 33166-3322</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>1 7862778309</t>
+        </is>
+      </c>
+      <c r="AC59" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BW-2026-063</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>BW260012</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Rachelle Huemoeller</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>54×25×28cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0.038 CBM</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>8</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
+        <v>326720</v>
+      </c>
+      <c r="U60" t="n">
+        <v>210000</v>
+      </c>
+      <c r="V60" t="n">
+        <v>116720</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>화장품 의약품</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>6279 Mahan drive, San Jose California 95123</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>1 (408) 807-1185</t>
+        </is>
+      </c>
+      <c r="AC60" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BW-2026-064</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BW260013</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Jacquline A</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>49×35×45cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0.079 CBM</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>17</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
+        <v>438000</v>
+      </c>
+      <c r="U61" t="n">
+        <v>387000</v>
+      </c>
+      <c r="V61" t="n">
+        <v>51000</v>
+      </c>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>1 (512) 773-6361</t>
+        </is>
+      </c>
+      <c r="AC61" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BW-2026-065</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BW260014</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>DAMIAN RENATO JESUS MALO JUVER</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>주식회사 비에프터</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>21×35×45cm(1CTN) / 49×35×45cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0.113 CBM</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>48</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T62" t="n">
+        <v>1096320</v>
+      </c>
+      <c r="U62" t="n">
+        <v>888000</v>
+      </c>
+      <c r="V62" t="n">
+        <v>208320</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>14411-B Export Rd,LAREDO TEXAS, USA,ZIP CODE 78045</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>1 8182189089</t>
+        </is>
+      </c>
+      <c r="AC62" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>47.8</v>
       </c>
     </row>
   </sheetData>

--- a/범운해운항공_전체데이터_통합백업_2026-10-20.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-20.xlsx
@@ -7962,7 +7962,11 @@
           <t>Jacquline A</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>항공(Air)</t>
@@ -8030,7 +8034,11 @@
         </is>
       </c>
       <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>555 Vwtrans Dr #201 Kyle,Tx 78640</t>
+        </is>
+      </c>
       <c r="AB61" t="inlineStr">
         <is>
           <t>1 (512) 773-6361</t>

--- a/범운해운항공_전체데이터_통합백업_2026-10-20.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-20.xlsx
@@ -7962,11 +7962,7 @@
           <t>Jacquline A</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>항공(Air)</t>
@@ -8198,7 +8194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8227,6 +8223,11 @@
           <t>적요</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>지급상태</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -8252,6 +8253,11 @@
           <t>통장잔액 법인통장</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>지급완료</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8277,6 +8283,11 @@
           <t>남양김태호 저녁식대</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>지급완료</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8302,6 +8313,11 @@
           <t>5710</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>지급완료</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8327,6 +8343,11 @@
           <t>아코 박수진 저녁식대</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>지급완료</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8352,6 +8373,11 @@
           <t>맥 이지훈 저녁식대</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>지급완료</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8377,6 +8403,11 @@
           <t>리턴의원 인천 용달비</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>지급완료</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8402,6 +8433,11 @@
           <t>넥서스 파마 고촌 용달입고비용</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>지급완료</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8427,6 +8463,11 @@
           <t>필러 20박스 윤세형 입고비용</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>지급완료</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8450,6 +8491,11 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>BFT 점심식사</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>미지급</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8835,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵", "에이블큐인터내셔널"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}, "에이블큐인터내셔널": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 48000, "추가단가": 48000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 48000, "추가단가": 48000, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "에이블큐인터내셔널": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "서광부장님", "전화번호": "nan", "주소": "서울 강서구 양천로24가길28-2"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "주식회사 비에프터"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "주식회사 비에프터": {"미국": {"항공(Air)": {"기타": {"기본중량": 1.0, "기본요금": 18500, "추가단가": 18500, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "김창화부사장", "전화번호": "010-6774-5216", "주소": "경기도 김포시 고촌읍 전호로 26번길 54 가동"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "주식회사 비에프터": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "김창화부사장", "전화번호": "010-6774-5216", "주소": "경기도 김포시 고촌읍 전호로 26번길 54 가동"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵", "에이블큐인터내셔널"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}, "에이블큐인터내셔널": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 48000, "추가단가": 48000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 48000, "추가단가": 48000, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "에이블큐인터내셔널": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "서광부장님", "전화번호": "nan", "주소": "서울 강서구 양천로24가길28-2"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "주식회사 비에프터"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "주식회사 비에프터": {"미국": {"항공(Air)": {"기타": {"기본중량": 1.0, "기본요금": 18500, "추가단가": 18500, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "김창화부사장", "전화번호": "010-6774-5216", "주소": "경기도 김포시 고촌읍 전호로 26번길 54 가동"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "주식회사 비에프터": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "김창화부사장", "전화번호": "010-6774-5216", "주소": "경기도 김포시 고촌읍 전호로 26번길 54 가동"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-20.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-20.xlsx
@@ -7962,7 +7962,11 @@
           <t>Jacquline A</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>케이글로발</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>항공(Air)</t>
@@ -8093,7 +8097,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>주식회사 비에프터</t>
+          <t>케이글로발</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8159,7 +8163,7 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr"/>
@@ -8835,7 +8839,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵", "에이블큐인터내셔널"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}, "에이블큐인터내셔널": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 48000, "추가단가": 48000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 48000, "추가단가": 48000, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "에이블큐인터내셔널": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "서광부장님", "전화번호": "nan", "주소": "서울 강서구 양천로24가길28-2"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "주식회사 비에프터"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "주식회사 비에프터": {"미국": {"항공(Air)": {"기타": {"기본중량": 1.0, "기본요금": 18500, "추가단가": 18500, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "김창화부사장", "전화번호": "010-6774-5216", "주소": "경기도 김포시 고촌읍 전호로 26번길 54 가동"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "주식회사 비에프터": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "김창화부사장", "전화번호": "010-6774-5216", "주소": "경기도 김포시 고촌읍 전호로 26번길 54 가동"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "케이글로발"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "케이글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18000, "추가단가": 18000, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "케이글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
     </row>
